--- a/NBFC-MF/Borrowers/Reena_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Reena_Weekly.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>2800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1217,42 +1217,44 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>2665.0766092382519</v>
+        <v>2018.5155583148735</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23" t="str">
+      <c r="A15" s="19">
+        <v>46289</v>
+      </c>
+      <c r="B15" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>53.438949076621675</v>
+      </c>
+      <c r="F15" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
+        <v>646.56105092337828</v>
+      </c>
+      <c r="G15" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>2018.5155583148735</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>7981.4844416851265</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>5</v>
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>7334.9233907617481</v>
+        <v>7981.4844416851265</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Reena_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Reena_Weekly.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>2100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>2018.5155583148735</v>
+        <v>4.5668002712773159E-10</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1254,35 +1254,37 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>7981.4844416851265</v>
+        <v>9999.9999999995434</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="22" t="str">
+      <c r="A16" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B16" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="1" t="str">
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="1"/>
+        <v>40.474390025879359</v>
+      </c>
+      <c r="F16" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G16" s="1" t="str">
+        <v>659.5256099741207</v>
+      </c>
+      <c r="G16" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H16" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>1358.9899483407528</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="2"/>
+        <v>8641.0100516592465</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -1293,31 +1295,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="23" t="str">
+      <c r="A17" s="19">
+        <v>46297</v>
+      </c>
+      <c r="B17" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
+        <v>27.249871314498439</v>
+      </c>
+      <c r="F17" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
+        <v>672.75012868550152</v>
+      </c>
+      <c r="G17" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>686.23981965525127</v>
+      </c>
+      <c r="H17" s="21">
+        <f t="shared" si="2"/>
+        <v>9313.7601803447487</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -1328,31 +1332,33 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="22" t="str">
+      <c r="A18" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B18" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="1" t="str">
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="1"/>
+        <v>13.760180345205463</v>
+      </c>
+      <c r="F18" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G18" s="1" t="str">
+        <v>686.23981965479459</v>
+      </c>
+      <c r="G18" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H18" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>4.5668002712773159E-10</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="2"/>
+        <v>9999.9999999995434</v>
       </c>
     </row>
   </sheetData>
